--- a/planogram/FORMULA PALLETS.xlsx
+++ b/planogram/FORMULA PALLETS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sverdlik\Desktop\WORKSPACE\PLANOGRAM MAHSAN FORMULA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sverdlik\Desktop\WORKSPACE\COLUMBUS\planogram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4244A1-8683-4F77-8256-D2296935F07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B91820-E581-497E-BBD8-D076A9EA4633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataSheet" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="541">
   <si>
     <t>מק"ט</t>
   </si>
@@ -1648,6 +1648,12 @@
   </si>
   <si>
     <t>PALLETS ספק</t>
+  </si>
+  <si>
+    <t>400004</t>
+  </si>
+  <si>
+    <t>סלט הרינג קצוץ "פארשמאק" 270גרם (6)NP</t>
   </si>
 </sst>
 </file>
@@ -1673,6 +1679,7 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1813,7 +1820,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1839,12 +1846,24 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="16">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2117,19 +2136,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{19E223FA-0EBF-4EF9-A888-13B8AF904124}" name="Table1" displayName="Table1" ref="A1:J233" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12" totalsRowBorderDxfId="11">
-  <autoFilter ref="A1:J233" xr:uid="{19E223FA-0EBF-4EF9-A888-13B8AF904124}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{19E223FA-0EBF-4EF9-A888-13B8AF904124}" name="Table1" displayName="Table1" ref="A1:J234" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:J234" xr:uid="{19E223FA-0EBF-4EF9-A888-13B8AF904124}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{07A3739E-5F56-4F69-934C-E76B73741FBF}" name="מק&quot;ט" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{ACD046D8-029D-4E24-85EF-F8AA7F7E9B5A}" name="ברקוד" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{01479DDE-C387-4BE4-8784-7A3A83185BCC}" name="תאור" dataDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{4C5DE09A-1EA6-44C7-9DA8-AED1BF7E745B}" name="משפחת מוצר" dataDxfId="7"/>
-    <tableColumn id="20" xr3:uid="{4A72721B-551B-4DDE-8F80-540B5871E47A}" name="תאור משפחה" dataDxfId="6"/>
-    <tableColumn id="68" xr3:uid="{9422F804-23BB-4DED-85D2-045DE64B2983}" name="סוג קטגוריה" dataDxfId="5"/>
-    <tableColumn id="69" xr3:uid="{5FBC3C45-06FF-4A0C-9C25-BEA529EAAE46}" name="מותג" dataDxfId="4"/>
-    <tableColumn id="118" xr3:uid="{B56213AD-390F-4CB6-B930-E897603B06C9}" name="משקל יחידה בק&quot;ג" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{0DF4D1AD-5606-4C1A-B268-19D022FC47B4}" name="PALLETS ספק" dataDxfId="2" dataCellStyle="Comma"/>
-    <tableColumn id="120" xr3:uid="{EE3DA846-585C-4F0F-91DE-FE3E68A13E66}" name="כמות קרטונים ב ASHDOD PALETT" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{07A3739E-5F56-4F69-934C-E76B73741FBF}" name="מק&quot;ט" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{ACD046D8-029D-4E24-85EF-F8AA7F7E9B5A}" name="ברקוד" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{01479DDE-C387-4BE4-8784-7A3A83185BCC}" name="תאור" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{4C5DE09A-1EA6-44C7-9DA8-AED1BF7E745B}" name="משפחת מוצר" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{4A72721B-551B-4DDE-8F80-540B5871E47A}" name="תאור משפחה" dataDxfId="7"/>
+    <tableColumn id="68" xr3:uid="{9422F804-23BB-4DED-85D2-045DE64B2983}" name="סוג קטגוריה" dataDxfId="6"/>
+    <tableColumn id="69" xr3:uid="{5FBC3C45-06FF-4A0C-9C25-BEA529EAAE46}" name="מותג" dataDxfId="5"/>
+    <tableColumn id="118" xr3:uid="{B56213AD-390F-4CB6-B930-E897603B06C9}" name="משקל יחידה בק&quot;ג" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{0DF4D1AD-5606-4C1A-B268-19D022FC47B4}" name="PALLETS ספק" dataDxfId="3" dataCellStyle="Comma"/>
+    <tableColumn id="120" xr3:uid="{EE3DA846-585C-4F0F-91DE-FE3E68A13E66}" name="כמות קרטונים ב ASHDOD PALETT" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2432,7 +2451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J233"/>
+  <dimension ref="A1:J234"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -9695,9 +9714,29 @@
         <v>81</v>
       </c>
     </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A234" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="B234" s="7"/>
+      <c r="C234" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="D234" s="7"/>
+      <c r="E234" s="7"/>
+      <c r="F234" s="7"/>
+      <c r="G234" s="7"/>
+      <c r="H234" s="8">
+        <v>0.27</v>
+      </c>
+      <c r="I234" s="14"/>
+      <c r="J234" s="19">
+        <v>238</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:F233">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="F2:F234">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
